--- a/Stats.xlsx
+++ b/Stats.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jakof-my.sharepoint.com/personal/andreas_jakof_eu/Documents/UntilTheEnd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{4435BF9B-1680-49F8-AF21-CC181DBFEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EDD6156-EC9F-4ACF-BF3F-2E11E96D3C6A}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{4435BF9B-1680-49F8-AF21-CC181DBFEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6184E2-914E-4F4F-8924-67F7EAF3E648}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A3D688E1-50A5-4922-B0AE-A46EBCE519BE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3D688E1-50A5-4922-B0AE-A46EBCE519BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -68,7 +68,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd\ hh:mm"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -100,7 +100,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -202,30 +202,36 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$3</c:f>
+              <c:f>Sheet1!$A$2:$A$4</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>46067.600694444445</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>46087</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$3</c:f>
+              <c:f>Sheet1!$B$2:$B$4</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17447</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18243</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -274,7 +280,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -485,29 +491,35 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$3</c:f>
+              <c:f>Sheet1!$A$2:$A$4</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>46067.600694444445</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>46087</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$3</c:f>
+              <c:f>Sheet1!$D$2:$D$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
@@ -557,7 +569,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -768,29 +780,35 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$3</c:f>
+              <c:f>Sheet1!$A$2:$A$4</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>46067.600694444445</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>46087</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$3</c:f>
+              <c:f>Sheet1!$E$2:$E$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
@@ -840,7 +858,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -1124,7 +1142,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -1407,7 +1425,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -1690,7 +1708,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -1903,30 +1921,36 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$3</c:f>
+              <c:f>Sheet1!$A$2:$A$4</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>46067.600694444445</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>46087</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$2:$H$3</c:f>
+              <c:f>Sheet1!$H$2:$H$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>65000</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>23622</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6574,7 +6598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{272A6D1D-E6A2-45C5-99B0-B2697FD31302}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.140625" style="1" bestFit="1" customWidth="1"/>
@@ -6660,6 +6684,32 @@
         <v>23622</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B4" s="2">
+        <v>18243</v>
+      </c>
+      <c r="C4">
+        <v>90</v>
+      </c>
+      <c r="D4">
+        <v>26</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>23653</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Stats.xlsx
+++ b/Stats.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jakof-my.sharepoint.com/personal/andreas_jakof_eu/Documents/UntilTheEnd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{4435BF9B-1680-49F8-AF21-CC181DBFEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6184E2-914E-4F4F-8924-67F7EAF3E648}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{4435BF9B-1680-49F8-AF21-CC181DBFEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{801C9DE0-52BA-4468-8066-F43D97EC189A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3D688E1-50A5-4922-B0AE-A46EBCE519BE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A3D688E1-50A5-4922-B0AE-A46EBCE519BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -213,7 +213,7 @@
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46087</c:v>
+                  <c:v>46088</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -231,7 +231,7 @@
                   <c:v>17447</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18243</c:v>
+                  <c:v>18805</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -502,7 +502,7 @@
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46087</c:v>
+                  <c:v>46088</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -791,7 +791,7 @@
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46087</c:v>
+                  <c:v>46088</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1932,7 +1932,7 @@
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46087</c:v>
+                  <c:v>46088</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="B4" s="2">
-        <v>18243</v>
+        <v>18805</v>
       </c>
       <c r="C4">
         <v>90</v>

--- a/Stats.xlsx
+++ b/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jakof-my.sharepoint.com/personal/andreas_jakof_eu/Documents/UntilTheEnd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{4435BF9B-1680-49F8-AF21-CC181DBFEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{801C9DE0-52BA-4468-8066-F43D97EC189A}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{4435BF9B-1680-49F8-AF21-CC181DBFEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3950EEF-4DCD-4048-8A20-34BA445DCCF9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A3D688E1-50A5-4922-B0AE-A46EBCE519BE}"/>
+    <workbookView minimized="1" xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{A3D688E1-50A5-4922-B0AE-A46EBCE519BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -213,7 +213,7 @@
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46088</c:v>
+                  <c:v>46088.720833333333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -231,7 +231,7 @@
                   <c:v>17447</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18805</c:v>
+                  <c:v>19772</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -502,7 +502,7 @@
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46088</c:v>
+                  <c:v>46088.720833333333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -791,7 +791,7 @@
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46088</c:v>
+                  <c:v>46088.720833333333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1932,7 +1932,7 @@
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46088</c:v>
+                  <c:v>46088.720833333333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>46088</v>
+        <v>46088.720833333333</v>
       </c>
       <c r="B4" s="2">
-        <v>18805</v>
+        <v>19772</v>
       </c>
       <c r="C4">
         <v>90</v>

--- a/Stats.xlsx
+++ b/Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jakof-my.sharepoint.com/personal/andreas_jakof_eu/Documents/UntilTheEnd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{4435BF9B-1680-49F8-AF21-CC181DBFEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3950EEF-4DCD-4048-8A20-34BA445DCCF9}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="8_{4435BF9B-1680-49F8-AF21-CC181DBFEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1B02F21-9D28-4E58-8560-82FFACBCC69D}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15345" xr2:uid="{A3D688E1-50A5-4922-B0AE-A46EBCE519BE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A3D688E1-50A5-4922-B0AE-A46EBCE519BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -231,7 +231,7 @@
                   <c:v>17447</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19772</c:v>
+                  <c:v>20024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -520,7 +520,7 @@
                   <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -809,7 +809,7 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6689,16 +6689,16 @@
         <v>46088.720833333333</v>
       </c>
       <c r="B4" s="2">
-        <v>19772</v>
+        <v>20024</v>
       </c>
       <c r="C4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>3</v>

--- a/Stats.xlsx
+++ b/Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jakof-my.sharepoint.com/personal/andreas_jakof_eu/Documents/UntilTheEnd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{4435BF9B-1680-49F8-AF21-CC181DBFEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1B02F21-9D28-4E58-8560-82FFACBCC69D}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{4435BF9B-1680-49F8-AF21-CC181DBFEE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F94B789-4914-4BA2-B36E-FFFD8DF3C6AE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A3D688E1-50A5-4922-B0AE-A46EBCE519BE}"/>
   </bookViews>
@@ -202,10 +202,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$4</c:f>
+              <c:f>Sheet1!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>46067.600694444445</c:v>
                 </c:pt>
@@ -215,15 +215,18 @@
                 <c:pt idx="2">
                   <c:v>46088.720833333333</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>46094.786805555559</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$4</c:f>
+              <c:f>Sheet1!$B$2:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -232,6 +235,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>20024</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25039</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -491,10 +497,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$4</c:f>
+              <c:f>Sheet1!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>46067.600694444445</c:v>
                 </c:pt>
@@ -504,15 +510,18 @@
                 <c:pt idx="2">
                   <c:v>46088.720833333333</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>46094.786805555559</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$4</c:f>
+              <c:f>Sheet1!$D$2:$D$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -521,6 +530,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -780,10 +792,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$4</c:f>
+              <c:f>Sheet1!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>46067.600694444445</c:v>
                 </c:pt>
@@ -793,15 +805,18 @@
                 <c:pt idx="2">
                   <c:v>46088.720833333333</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>46094.786805555559</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$4</c:f>
+              <c:f>Sheet1!$E$2:$E$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -810,6 +825,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1070,30 +1088,42 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$3</c:f>
+              <c:f>Sheet1!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>46067.600694444445</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>46088.720833333333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46094.786805555559</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$3</c:f>
+              <c:f>Sheet1!$C$2:$C$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>110</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1353,29 +1383,41 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$3</c:f>
+              <c:f>Sheet1!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>46067.600694444445</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>46088.720833333333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46094.786805555559</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$3</c:f>
+              <c:f>Sheet1!$F$2:$F$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
@@ -1636,29 +1678,41 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$3</c:f>
+              <c:f>Sheet1!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>46067.600694444445</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>46085.472222222219</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>46088.720833333333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46094.786805555559</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$3</c:f>
+              <c:f>Sheet1!$G$2:$G$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
@@ -1921,10 +1975,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$4</c:f>
+              <c:f>Sheet1!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>46067.600694444445</c:v>
                 </c:pt>
@@ -1934,15 +1988,18 @@
                 <c:pt idx="2">
                   <c:v>46088.720833333333</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>46094.786805555559</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$2:$H$4</c:f>
+              <c:f>Sheet1!$H$2:$H$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>65000</c:v>
                 </c:pt>
@@ -1951,6 +2008,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>23653</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6598,7 +6658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{272A6D1D-E6A2-45C5-99B0-B2697FD31302}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.140625" style="1" bestFit="1" customWidth="1"/>
@@ -6710,6 +6770,32 @@
         <v>23653</v>
       </c>
     </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>46094.786805555559</v>
+      </c>
+      <c r="B5" s="2">
+        <v>25039</v>
+      </c>
+      <c r="C5">
+        <v>110</v>
+      </c>
+      <c r="D5">
+        <v>37</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>23798</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
